--- a/data/raw/sales/Week 30/Nexlev/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 30/Nexlev/Seller Sales (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5951,17 +5951,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA78980</t>
+          <t>FBA80111</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0GYSS16FJ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0GYSS16FJ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5971,27 +5971,27 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GS-02</t>
+          <t>MR-01_Part</t>
         </is>
       </c>
       <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
         <v>3</v>
       </c>
-      <c r="G93" t="n">
-        <v>5666.95</v>
-      </c>
-      <c r="H93" t="n">
-        <v>814</v>
-      </c>
       <c r="I93" t="n">
-        <v>1192</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>47.28</v>
+        <v>100</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>NEXLEV</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -6011,17 +6011,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6031,23 +6031,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" t="n">
-        <v>7049.15</v>
+        <v>5666.95</v>
       </c>
       <c r="H94" t="n">
-        <v>5338</v>
+        <v>814</v>
       </c>
       <c r="I94" t="n">
-        <v>7463</v>
+        <v>1192</v>
       </c>
       <c r="J94" t="n">
-        <v>1.47</v>
+        <v>47.28</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -6071,17 +6071,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79229</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6091,23 +6091,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>7049.15</v>
       </c>
       <c r="H95" t="n">
-        <v>17</v>
+        <v>5338</v>
       </c>
       <c r="I95" t="n">
-        <v>22</v>
+        <v>7463</v>
       </c>
       <c r="J95" t="n">
-        <v>57.14</v>
+        <v>1.47</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -6131,17 +6131,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79229</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6151,23 +6151,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MR-01</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>76525.42</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>23801</v>
+        <v>17</v>
       </c>
       <c r="I96" t="n">
-        <v>29080</v>
+        <v>22</v>
       </c>
       <c r="J96" t="n">
-        <v>57.08</v>
+        <v>57.14</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -6191,17 +6191,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6211,23 +6211,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>MR-01</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>76525.42</v>
       </c>
       <c r="H97" t="n">
-        <v>55</v>
+        <v>23801</v>
       </c>
       <c r="I97" t="n">
-        <v>69</v>
+        <v>29080</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>57.08</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -6251,17 +6251,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -6281,10 +6281,10 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="I98" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -6311,17 +6311,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6341,13 +6341,13 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>1015</v>
+        <v>14</v>
       </c>
       <c r="I99" t="n">
-        <v>1399</v>
+        <v>20</v>
       </c>
       <c r="J99" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -6371,17 +6371,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -6401,13 +6401,13 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>254</v>
+        <v>1015</v>
       </c>
       <c r="I100" t="n">
-        <v>302</v>
+        <v>1399</v>
       </c>
       <c r="J100" t="n">
-        <v>45.96</v>
+        <v>3.53</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -6431,17 +6431,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6461,13 +6461,13 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="I101" t="n">
-        <v>93</v>
+        <v>302</v>
       </c>
       <c r="J101" t="n">
-        <v>51.16</v>
+        <v>45.96</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -6491,17 +6491,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6511,23 +6511,23 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>1937.29</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>453</v>
+        <v>77</v>
       </c>
       <c r="I102" t="n">
-        <v>605</v>
+        <v>93</v>
       </c>
       <c r="J102" t="n">
-        <v>4.09</v>
+        <v>51.16</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -6551,17 +6551,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6571,23 +6571,23 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1937.29</v>
       </c>
       <c r="H103" t="n">
-        <v>233</v>
+        <v>453</v>
       </c>
       <c r="I103" t="n">
-        <v>279</v>
+        <v>605</v>
       </c>
       <c r="J103" t="n">
-        <v>0.37</v>
+        <v>4.09</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -6611,17 +6611,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6631,23 +6631,23 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>1523.73</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>131</v>
+        <v>233</v>
       </c>
       <c r="I104" t="n">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="J104" t="n">
-        <v>96.53</v>
+        <v>0.37</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -6671,17 +6671,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6691,23 +6691,23 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>5081.36</v>
+        <v>1523.73</v>
       </c>
       <c r="H105" t="n">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="I105" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="J105" t="n">
-        <v>59.32</v>
+        <v>96.53</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -6731,17 +6731,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6751,23 +6751,23 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SW-01</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>5081.36</v>
       </c>
       <c r="H106" t="n">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="I106" t="n">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="J106" t="n">
-        <v>0.45</v>
+        <v>59.32</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -6791,17 +6791,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>SW-01</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>457</v>
+        <v>191</v>
       </c>
       <c r="I107" t="n">
-        <v>598</v>
+        <v>265</v>
       </c>
       <c r="J107" t="n">
-        <v>27.53</v>
+        <v>0.45</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -6851,17 +6851,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6871,23 +6871,23 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>4360.17</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>160</v>
+        <v>457</v>
       </c>
       <c r="I108" t="n">
-        <v>202</v>
+        <v>598</v>
       </c>
       <c r="J108" t="n">
-        <v>53.49</v>
+        <v>27.53</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -6911,17 +6911,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6931,23 +6931,23 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>4360.17</v>
       </c>
       <c r="H109" t="n">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="I109" t="n">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="J109" t="n">
-        <v>42.16</v>
+        <v>53.49</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -6971,17 +6971,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79452</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6991,23 +6991,23 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>VC-01</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>68103.39</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>2304</v>
+        <v>224</v>
       </c>
       <c r="I110" t="n">
-        <v>3264</v>
+        <v>301</v>
       </c>
       <c r="J110" t="n">
-        <v>99.58</v>
+        <v>42.16</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -7031,17 +7031,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79452</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7051,23 +7051,23 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>VC-01</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="G111" t="n">
-        <v>16651.69</v>
+        <v>68103.39</v>
       </c>
       <c r="H111" t="n">
-        <v>576</v>
+        <v>2304</v>
       </c>
       <c r="I111" t="n">
-        <v>901</v>
+        <v>3264</v>
       </c>
       <c r="J111" t="n">
-        <v>38.87</v>
+        <v>99.58</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -7091,17 +7091,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7111,23 +7111,23 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>16651.69</v>
       </c>
       <c r="H112" t="n">
-        <v>218</v>
+        <v>576</v>
       </c>
       <c r="I112" t="n">
-        <v>261</v>
+        <v>901</v>
       </c>
       <c r="J112" t="n">
-        <v>55.74</v>
+        <v>38.87</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -7151,17 +7151,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7171,23 +7171,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>2995.76</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>11565</v>
+        <v>218</v>
       </c>
       <c r="I113" t="n">
-        <v>14064</v>
+        <v>261</v>
       </c>
       <c r="J113" t="n">
-        <v>2.35</v>
+        <v>55.74</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -7211,17 +7211,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7231,23 +7231,23 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>2995.76</v>
       </c>
       <c r="H114" t="n">
-        <v>255</v>
+        <v>11565</v>
       </c>
       <c r="I114" t="n">
-        <v>322</v>
+        <v>14064</v>
       </c>
       <c r="J114" t="n">
-        <v>1.34</v>
+        <v>2.35</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -7271,17 +7271,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -7301,13 +7301,13 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>321</v>
+        <v>255</v>
       </c>
       <c r="I115" t="n">
-        <v>480</v>
+        <v>322</v>
       </c>
       <c r="J115" t="n">
-        <v>0.5</v>
+        <v>1.34</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -7331,17 +7331,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -7361,13 +7361,13 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
+        <v>321</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>480</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -7391,17 +7391,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -7421,13 +7421,13 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="J117" t="n">
-        <v>35.53</v>
+        <v>0</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -7451,17 +7451,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79566</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7471,23 +7471,23 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>VC-05</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>2202.54</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="I118" t="n">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="J118" t="n">
-        <v>12.3</v>
+        <v>35.53</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -7511,17 +7511,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7531,23 +7531,23 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>2643.22</v>
+        <v>2202.54</v>
       </c>
       <c r="H119" t="n">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="I119" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="J119" t="n">
-        <v>100</v>
+        <v>12.3</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -7571,17 +7571,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7591,23 +7591,23 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>68734.75</v>
+        <v>2643.22</v>
       </c>
       <c r="H120" t="n">
-        <v>6358</v>
+        <v>37</v>
       </c>
       <c r="I120" t="n">
-        <v>8993</v>
+        <v>66</v>
       </c>
       <c r="J120" t="n">
-        <v>16.29</v>
+        <v>100</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -7631,17 +7631,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7651,23 +7651,23 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>68734.75</v>
       </c>
       <c r="H121" t="n">
-        <v>214</v>
+        <v>6358</v>
       </c>
       <c r="I121" t="n">
-        <v>252</v>
+        <v>8993</v>
       </c>
       <c r="J121" t="n">
-        <v>14.86</v>
+        <v>16.29</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -7691,17 +7691,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -7721,13 +7721,13 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>3313</v>
+        <v>214</v>
       </c>
       <c r="I122" t="n">
-        <v>5152</v>
+        <v>252</v>
       </c>
       <c r="J122" t="n">
-        <v>0.09</v>
+        <v>14.86</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -7751,17 +7751,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7771,23 +7771,23 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>11015.25</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>1347</v>
+        <v>3313</v>
       </c>
       <c r="I123" t="n">
-        <v>1872</v>
+        <v>5152</v>
       </c>
       <c r="J123" t="n">
-        <v>14.25</v>
+        <v>0.09</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -7811,17 +7811,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7831,23 +7831,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>11015.25</v>
       </c>
       <c r="H124" t="n">
-        <v>85</v>
+        <v>1347</v>
       </c>
       <c r="I124" t="n">
-        <v>113</v>
+        <v>1872</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -7871,17 +7871,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7901,13 +7901,13 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="I125" t="n">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="J125" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -7931,17 +7931,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7951,23 +7951,23 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>154193.22</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>15328</v>
+        <v>29</v>
       </c>
       <c r="I126" t="n">
-        <v>21171</v>
+        <v>29</v>
       </c>
       <c r="J126" t="n">
-        <v>47.45</v>
+        <v>100</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -7991,17 +7991,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8011,23 +8011,23 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ETC-07-WH</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>154193.22</v>
       </c>
       <c r="H127" t="n">
-        <v>98</v>
+        <v>15328</v>
       </c>
       <c r="I127" t="n">
-        <v>133</v>
+        <v>21171</v>
       </c>
       <c r="J127" t="n">
-        <v>7.2</v>
+        <v>47.45</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -8051,17 +8051,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8071,23 +8071,23 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1053</v>
+        <v>98</v>
       </c>
       <c r="I128" t="n">
-        <v>1410</v>
+        <v>133</v>
       </c>
       <c r="J128" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -8111,17 +8111,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8131,23 +8131,23 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>32</v>
+        <v>1053</v>
       </c>
       <c r="I129" t="n">
-        <v>40</v>
+        <v>1410</v>
       </c>
       <c r="J129" t="n">
-        <v>44.44</v>
+        <v>1.05</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -8171,17 +8171,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -8201,13 +8201,13 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>27434</v>
+        <v>32</v>
       </c>
       <c r="I130" t="n">
-        <v>35682</v>
+        <v>40</v>
       </c>
       <c r="J130" t="n">
-        <v>0.07000000000000001</v>
+        <v>44.44</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -8231,17 +8231,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBK80024</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -8261,13 +8261,13 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>265</v>
+        <v>27434</v>
       </c>
       <c r="I131" t="n">
-        <v>374</v>
+        <v>35682</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -8291,17 +8291,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBM79991</t>
+          <t>FBK80024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8311,23 +8311,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>66428.81</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>3425</v>
+        <v>265</v>
       </c>
       <c r="I132" t="n">
-        <v>4760</v>
+        <v>374</v>
       </c>
       <c r="J132" t="n">
-        <v>8.99</v>
+        <v>0</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -8351,17 +8351,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79989</t>
+          <t>FBM79991</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8371,23 +8371,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CAP-05</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>66428.81</v>
       </c>
       <c r="H133" t="n">
-        <v>72</v>
+        <v>3425</v>
       </c>
       <c r="I133" t="n">
-        <v>113</v>
+        <v>4760</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>8.99</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -8411,17 +8411,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBA79989</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>CAP-05</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -8441,13 +8441,13 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>3189</v>
+        <v>72</v>
       </c>
       <c r="I134" t="n">
-        <v>4059</v>
+        <v>113</v>
       </c>
       <c r="J134" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -8471,58 +8471,118 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>FBA79993</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>B0GN8WW6BC</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ST-03</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3189</v>
+      </c>
+      <c r="I135" t="n">
+        <v>4059</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>VIOMI</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>30</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>FBA79992</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>B0GN94YDY2</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>B0GN94YDY2</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>ST-02</t>
         </is>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
         <v>616</v>
       </c>
-      <c r="I135" t="n">
+      <c r="I136" t="n">
         <v>860</v>
       </c>
-      <c r="J135" t="n">
+      <c r="J136" t="n">
         <v>0.13</v>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="K136" t="inlineStr">
         <is>
           <t>VIOMI</t>
         </is>
       </c>
-      <c r="L135" t="n">
-        <v>30</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
+      <c r="L136" t="n">
+        <v>30</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>

--- a/data/raw/sales/Week 30/Nexlev/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 30/Nexlev/Seller Sales (SP-API).xlsx
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>2539.83</v>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>6437.29</v>
+        <v>4827.97</v>
       </c>
       <c r="H63" t="n">
         <v>85</v>
